--- a/Regelsæt.xlsx
+++ b/Regelsæt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\RPA\Leverancer\Påmindelse om afregning af indsatser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C589E0A5-E979-4F4E-8FDD-351252D22866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8940157-DA20-4F7B-9289-45A70164E63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,18 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Organisation</t>
   </si>
   <si>
     <t>Status på indsats</t>
-  </si>
-  <si>
-    <t>CFU Familierådgivningen</t>
-  </si>
-  <si>
-    <t>CFU Familierådgivningen - Rådgivere</t>
   </si>
   <si>
     <t>Bestilt</t>
@@ -58,57 +52,15 @@
 </t>
   </si>
   <si>
-    <t>Ungerådgivningen - Særlig funktion</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Ungerådgivningen Social 1 - Vagt &amp; Visitation</t>
   </si>
   <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Ungerådgivningen Special - Kompensation</t>
   </si>
   <si>
-    <t>Ungerådgivningen Special - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Forebyggende Indsatser</t>
-  </si>
-  <si>
     <t>Irrelevante leverandører</t>
   </si>
   <si>
-    <t>Kontaktperson og Bostøtte Unge 1</t>
-  </si>
-  <si>
-    <t>Kontaktperson og Bostøtte Unge 2</t>
-  </si>
-  <si>
-    <t>Kontaktperson og Bostøtte Unge 3</t>
-  </si>
-  <si>
-    <t>Kontaktperson og Bostøtte Unge 4</t>
-  </si>
-  <si>
     <t>Paragraffer til Løn og Personale</t>
   </si>
   <si>
@@ -116,6 +68,42 @@
   </si>
   <si>
     <t>Servicelov | § 42</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 1</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 2</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 3</t>
+  </si>
+  <si>
+    <t>Familierådgivningen</t>
+  </si>
+  <si>
+    <t>Kriminalpræventive Indsatser</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 1</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 2</t>
+  </si>
+  <si>
+    <t>Famiivesatsil Familierådgivningen</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 1 - Vagt &amp; Visitation</t>
+  </si>
+  <si>
+    <t>Ungeindsatser Kompensation</t>
+  </si>
+  <si>
+    <t>Krimveasatsmi Indsatser</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 3</t>
   </si>
 </sst>
 </file>
@@ -445,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.85546875" customWidth="1"/>
@@ -459,134 +447,81 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" t="s">
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
